--- a/data/trans_orig/IP1010-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Provincia-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102989</t>
+          <t>103489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205070</t>
+          <t>205017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209681</t>
+          <t>210319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132022</t>
+          <t>131329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>259775</t>
+          <t>260656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153540</t>
+          <t>153603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159233</t>
+          <t>158991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315521</t>
+          <t>315541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>676698</t>
+          <t>676661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>713425</t>
+          <t>712767</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>720686</t>
+          <t>720693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1393161</t>
+          <t>1393096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401086</t>
+          <t>1401003</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67121</t>
+          <t>67313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134496</t>
+          <t>135301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72609</t>
+          <t>72395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155780</t>
+          <t>155054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>42810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86757</t>
+          <t>86733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111480</t>
+          <t>111560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142625</t>
+          <t>142408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280893</t>
+          <t>281118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>700966</t>
+          <t>700500</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>706928</t>
+          <t>706485</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>741411</t>
+          <t>741797</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>747454</t>
+          <t>747456</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1445911</t>
+          <t>1445480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453079</t>
+          <t>1453105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>72542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79689</t>
+          <t>79122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149378</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156167</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161279</t>
+          <t>161236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167188</t>
+          <t>167231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331072</t>
+          <t>330608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701388</t>
+          <t>701773</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>734707</t>
+          <t>734287</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>742665</t>
+          <t>742673</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1438415</t>
+          <t>1439127</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1446572</t>
+          <t>1446657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1010-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106800</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108126</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>106800</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103489</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108116</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205017</t>
+          <t>205079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210319</t>
+          <t>209678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150554</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,84 +2780,84 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>725</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134930</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131474</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134930</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>131329</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260656</t>
+          <t>260660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3128,102 +3128,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4301</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4355</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5873</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3236,107 +3236,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162755</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>159831</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>156657</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>153603</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>153549</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162755</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>158991</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>319412</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>316089</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>321351</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>319412</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>315541</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>321262</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,74 +3466,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9829</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>718042</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>712871</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>720694</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679774</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>676661</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>676644</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>718042</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>712767</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>720693</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2095</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1393096</t>
+          <t>1393079</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401003</t>
+          <t>1401019</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>691</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3461</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4844,72 +4844,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69893</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69893</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67313</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135301</t>
+          <t>134822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5366</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5192,69 +5192,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>76422</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72395</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73193</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155054</t>
+          <t>154819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3273</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5530,72 +5530,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45458</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42766</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45458</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42810</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86733</t>
+          <t>86191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5765,102 +5765,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1443</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4670</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5873,74 +5873,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55229</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>52882</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>51748</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111560</t>
+          <t>111548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3339</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6216,72 +6216,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145115</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>142175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145115</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142408</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281118</t>
+          <t>281364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6345</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>745493</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>742120</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>747492</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704833</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>700500</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>699827</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706485</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>745493</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>741797</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>747456</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2077</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1445480</t>
+          <t>1445881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453105</t>
+          <t>1453298</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,92 +8397,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>4332</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8642</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -8510,72 +8510,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76852</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72386</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79751</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>76852</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>72542</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79122</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148794</t>
+          <t>149337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156036</t>
+          <t>156651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9774,102 +9774,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2940</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3618</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4417</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -9882,74 +9882,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170124</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167216</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>163652</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>161236</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>161534</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170124</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167231</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>514</t>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330608</t>
+          <t>330876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10311</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>739787</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>734533</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>742652</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>703847</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>701773</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>701244</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>739787</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>734287</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>742673</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2118</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1439127</t>
+          <t>1438214</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1446657</t>
+          <t>1446552</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
